--- a/data/Mock Data - FindDee (Fake) V2.xlsx
+++ b/data/Mock Data - FindDee (Fake) V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wichitv\Desktop\อบรม AI\FindDee\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5832C913-64C4-4187-867C-0D005F9B6EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7167E7-5BCD-4ADF-B9F9-FA514D5815E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="266">
   <si>
     <t>Cus ID</t>
   </si>
@@ -841,117 +841,6 @@
   </si>
   <si>
     <t>บริษัท</t>
-  </si>
-  <si>
-    <t>2998501</t>
-  </si>
-  <si>
-    <t>2998502</t>
-  </si>
-  <si>
-    <t>2998503</t>
-  </si>
-  <si>
-    <t>2998504</t>
-  </si>
-  <si>
-    <t>2998505</t>
-  </si>
-  <si>
-    <t>2998506</t>
-  </si>
-  <si>
-    <t>9430816</t>
-  </si>
-  <si>
-    <t>9430817</t>
-  </si>
-  <si>
-    <t>9430818</t>
-  </si>
-  <si>
-    <t>9430819</t>
-  </si>
-  <si>
-    <t>9430820</t>
-  </si>
-  <si>
-    <t>9430821</t>
-  </si>
-  <si>
-    <t>2721961</t>
-  </si>
-  <si>
-    <t>2721962</t>
-  </si>
-  <si>
-    <t>2721963</t>
-  </si>
-  <si>
-    <t>2721964</t>
-  </si>
-  <si>
-    <t>2721965</t>
-  </si>
-  <si>
-    <t>2721966</t>
-  </si>
-  <si>
-    <t>8056748</t>
-  </si>
-  <si>
-    <t>8056749</t>
-  </si>
-  <si>
-    <t>8056750</t>
-  </si>
-  <si>
-    <t>8056751</t>
-  </si>
-  <si>
-    <t>8056752</t>
-  </si>
-  <si>
-    <t>9236010</t>
-  </si>
-  <si>
-    <t>9236011</t>
-  </si>
-  <si>
-    <t>9236012</t>
-  </si>
-  <si>
-    <t>8400347</t>
-  </si>
-  <si>
-    <t>8400348</t>
-  </si>
-  <si>
-    <t>8400349</t>
-  </si>
-  <si>
-    <t>8400350</t>
-  </si>
-  <si>
-    <t>8400351</t>
-  </si>
-  <si>
-    <t>8400352</t>
-  </si>
-  <si>
-    <t>1042528</t>
-  </si>
-  <si>
-    <t>1042529</t>
-  </si>
-  <si>
-    <t>2354319</t>
-  </si>
-  <si>
-    <t>2354320</t>
-  </si>
-  <si>
-    <t>2354321</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1290,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>266</v>
+        <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -1415,7 +1304,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>267</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>5</v>
@@ -1429,7 +1318,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>268</v>
+        <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>5</v>
@@ -1443,7 +1332,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>269</v>
+        <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>5</v>
@@ -1457,7 +1346,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>270</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>5</v>
@@ -1471,7 +1360,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>271</v>
+        <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -1499,7 +1388,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>272</v>
+        <v>7</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
@@ -1513,7 +1402,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>273</v>
+        <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
@@ -1527,7 +1416,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>274</v>
+        <v>7</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>8</v>
@@ -1541,7 +1430,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>275</v>
+        <v>7</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>8</v>
@@ -1555,7 +1444,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>8</v>
@@ -1569,7 +1458,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>277</v>
+        <v>7</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>8</v>
@@ -1597,7 +1486,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>278</v>
+        <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>11</v>
@@ -1611,7 +1500,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>279</v>
+        <v>10</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>11</v>
@@ -1625,7 +1514,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>11</v>
@@ -1639,7 +1528,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>281</v>
+        <v>10</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>11</v>
@@ -1653,7 +1542,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>282</v>
+        <v>10</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>11</v>
@@ -1667,7 +1556,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>283</v>
+        <v>10</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>11</v>
@@ -1695,7 +1584,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>284</v>
+        <v>13</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>14</v>
@@ -1709,7 +1598,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>285</v>
+        <v>13</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
@@ -1723,7 +1612,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>286</v>
+        <v>13</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>14</v>
@@ -1737,7 +1626,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>287</v>
+        <v>13</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>14</v>
@@ -1751,7 +1640,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>288</v>
+        <v>13</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>14</v>
@@ -1765,7 +1654,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>17</v>
@@ -1779,7 +1668,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>289</v>
+        <v>13</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>17</v>
@@ -1793,7 +1682,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>290</v>
+        <v>13</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
@@ -1807,7 +1696,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>291</v>
+        <v>13</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>17</v>
@@ -1835,7 +1724,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>292</v>
+        <v>19</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>20</v>
@@ -1849,7 +1738,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>20</v>
@@ -1863,7 +1752,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>294</v>
+        <v>19</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>20</v>
@@ -1877,7 +1766,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>20</v>
@@ -1891,7 +1780,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>20</v>
@@ -1905,7 +1794,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>20</v>
@@ -1918,8 +1807,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
-        <v>22</v>
+      <c r="A40" s="6">
+        <v>1042527</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>23</v>
@@ -1933,7 +1822,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>298</v>
+        <v>22</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>23</v>
@@ -1947,7 +1836,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>23</v>
@@ -1975,7 +1864,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>26</v>
@@ -1989,7 +1878,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>301</v>
+        <v>25</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>26</v>
@@ -2003,7 +1892,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>302</v>
+        <v>25</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>26</v>

--- a/data/Mock Data - FindDee (Fake) V2.xlsx
+++ b/data/Mock Data - FindDee (Fake) V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wichitv\Desktop\อบรม AI\FindDee\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7167E7-5BCD-4ADF-B9F9-FA514D5815E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072F64AF-A023-41FD-9C24-E5398ACDFA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,6 +42,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Wichit Visedsinthop</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{7F2C1216-10FC-4E60-9C88-2EF5FA28D693}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t>Wichit Visedsinthop:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="222"/>
+          </rPr>
+          <t xml:space="preserve">
+ถ้าเจอแสดงว่าพบ
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="266">
   <si>
@@ -850,7 +885,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -869,6 +904,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="222"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1250,7 +1298,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1908,6 +1956,7 @@
   <autoFilter ref="A1:D46" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
